--- a/GroceryApplicationProject/src/test/resources/TestData.xlsx
+++ b/GroceryApplicationProject/src/test/resources/TestData.xlsx
@@ -4,18 +4,19 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="LoginPage" sheetId="1" r:id="rId1"/>
     <sheet name="AdminUsersPage" sheetId="2" r:id="rId2"/>
+    <sheet name="ManageNewsPage" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
   <si>
     <t>admin</t>
   </si>
@@ -33,6 +34,9 @@
   </si>
   <si>
     <t>s@123</t>
+  </si>
+  <si>
+    <t>New product launched1</t>
   </si>
 </sst>
 </file>
@@ -456,4 +460,22 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="21.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>